--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,140 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>D181</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Severe complicated COVID-19</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>新冠并发重症</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>15</v>
       </c>
-      <c r="N2" t="n">
-        <v>3.387096774193548</v>
-      </c>
       <c r="O2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.06518538669655344</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -690,97 +878,212 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>D181</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Severe complicated COVID-19</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>新冠并发重症</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>5</v>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="N3" t="n">
-        <v>1.129032258064516</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.02172846223218448</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -809,97 +1112,140 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>D181</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Severe complicated COVID-19</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>新冠并发重症</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>13</v>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
-        <v>0.05649400180367965</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="n">
+        <v>0.02172846223218448</v>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -928,97 +1274,212 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>D181</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Severe complicated COVID-19</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>新冠并发重症</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>3</v>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="N5" t="n">
-        <v>0.6774193548387096</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.01303707733931069</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1047,97 +1508,140 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>D181</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Severe complicated COVID-19</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>新冠并发重症</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>6</v>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
       </c>
       <c r="N6" t="n">
-        <v>1.4</v>
+        <v>13</v>
       </c>
       <c r="O6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
-        <v>0.02607415467862137</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="n">
+        <v>0.05649400180367965</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1166,97 +1670,212 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>D181</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Severe complicated COVID-19</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>新冠并发重症</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>38</v>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
       </c>
       <c r="N7" t="n">
-        <v>8.580645161290322</v>
+        <v>13</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.165136312964602</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
+        <v>13</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1285,97 +1904,140 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>D181</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Severe complicated COVID-19</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>新冠并发重症</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>168</v>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
       </c>
       <c r="N8" t="n">
-        <v>39.2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="n">
-        <v>0.7300763310013986</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="n">
+        <v>0.01303707733931069</v>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1404,97 +2066,1796 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>D181</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Severe complicated COVID-19</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>新冠并发重症</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>severe-complicated-covid-19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>新冠并发重症</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.02607415467862137</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>severe-complicated-covid-19</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>新冠并发重症</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>severe-complicated-covid-19</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>新冠并发重症</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>38</v>
+      </c>
+      <c r="O12" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.165136312964602</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>severe-complicated-covid-19</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>新冠并发重症</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>38</v>
+      </c>
+      <c r="O13" t="n">
+        <v>38</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>severe-complicated-covid-19</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>新冠并发重症</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>169</v>
+      </c>
+      <c r="O14" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.7344220234478355</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>severe-complicated-covid-19</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>新冠并发重症</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>169</v>
+      </c>
+      <c r="O15" t="n">
+        <v>169</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>severe-complicated-covid-19</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>新冠并发重症</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>29</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.548387096774193</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="N16" t="n">
+        <v>50</v>
+      </c>
+      <c r="O16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="n">
-        <v>0.12602508094667</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R16" t="n">
+        <v>0.2172846223218448</v>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AW16" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BA16" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BB16" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>severe-complicated-covid-19</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Severe complicated COVID-19</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>新冠并发重症</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>50</v>
+      </c>
+      <c r="O17" t="n">
+        <v>50</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1612,7 +3973,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1622,52 +3983,94 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>277</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="O16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2172846223218448</v>
+        <v>0.2390130845540293</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="O17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="O16" t="n">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2390130845540293</v>
+        <v>0.3954580126257575</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="O17" t="n">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>304</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="O16" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3954580126257575</v>
+        <v>0.4519520144294372</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="O17" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -1953,9 +1953,6 @@
       <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.01303707733931069</v>
       </c>
@@ -2202,7 +2199,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2349,9 +2346,6 @@
       <c r="O10" t="n">
         <v>6</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.02607415467862137</v>
       </c>
@@ -2598,7 +2592,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2745,9 +2739,6 @@
       <c r="O12" t="n">
         <v>38</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.165136312964602</v>
       </c>
@@ -2994,7 +2985,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3141,9 +3132,6 @@
       <c r="O14" t="n">
         <v>169</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.7344220234478355</v>
       </c>
@@ -3390,7 +3378,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3532,16 +3520,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4519520144294372</v>
+        <v>0.5171374011259906</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3694,10 +3679,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="O17" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3786,7 +3771,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4039,7 +4024,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>353</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -3520,13 +3520,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="O16" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5171374011259906</v>
+        <v>0.5910141727154179</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="O17" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>368</v>
+        <v>385</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -3520,13 +3520,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="O16" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5910141727154179</v>
+        <v>0.6214340198404762</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="O17" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -3520,13 +3520,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="O16" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6214340198404762</v>
+        <v>0.7387677158942723</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="O17" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>392</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">

--- a/diseases/d181/2026-2029.xlsx
+++ b/diseases/d181/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
